--- a/input/excel/Profile and ValueSet_Specimen_15.01.2025_v1.csv/RelevantClinicalInformationVS.xlsx
+++ b/input/excel/Profile and ValueSet_Specimen_15.01.2025_v1.csv/RelevantClinicalInformationVS.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\behzod_axmedov\Desktop\DHP-temp02\UZCoreSpecimen\digital-health-ig\input\excel\Profile and ValueSet_Specimen_15.01.2025_v1.csv\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D0E8789-8718-4621-9E6A-8D3F926862C8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="7725" yWindow="2625" windowWidth="12615" windowHeight="10230" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -24,77 +18,9 @@
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
-  <si>
-    <t>CODE</t>
-  </si>
-  <si>
-    <t>EN</t>
-  </si>
-  <si>
-    <t>RU</t>
-  </si>
-  <si>
-    <t>UZ</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/CodeSystem/v2-0916</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>Patient was fasting prior to the procedure.</t>
-  </si>
-  <si>
-    <t>Пациент был натощак перед процедурой.</t>
-  </si>
-  <si>
-    <t>Bemor protsedura oldidan och qoringa edi.</t>
-  </si>
-  <si>
-    <t>NF</t>
-  </si>
-  <si>
-    <t>The patient indicated they did not fast prior to the procedure</t>
-  </si>
-  <si>
-    <t>Пациент сообщил, что не соблюдал голодание перед процедурой.</t>
-  </si>
-  <si>
-    <t>Bemor protsedura oldidan och qoringa bo‘lmaganini bildirdi.</t>
-  </si>
-  <si>
-    <t>NG</t>
-  </si>
-  <si>
-    <t>Not Given - Patient was not asked at the time of the procedure.</t>
-  </si>
-  <si>
-    <t>Не указано — пациента не спрашивали во время процедуры.</t>
-  </si>
-  <si>
-    <t>Ko‘rsatilmagan protsedura vaqtida bemordan so‘ralmagan.</t>
-  </si>
-  <si>
-    <t>FNA</t>
-  </si>
-  <si>
-    <t>Fasting not asked of the patient at time of procedure.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Информация о голодании не была запрошена у пациента во время </t>
-  </si>
-  <si>
-    <t>Protsedura vaqtida bemordan och qoringa bo‘lishi haqida so‘ralmagan.</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -102,51 +28,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF333333"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <charset val="204"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -154,41 +45,15 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 2" xfId="1" xr:uid="{F24BE4C9-0C24-4FD3-96C1-1A0C0D87AB19}"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -465,94 +330,10 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="34.28515625" customWidth="1"/>
-    <col min="3" max="3" width="29" customWidth="1"/>
-    <col min="4" max="4" width="35.5703125" customWidth="1"/>
-    <col min="5" max="5" width="36.42578125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="3"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="3"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="3"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" s="3"/>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>